--- a/test/standard_mapping/output.xlsx
+++ b/test/standard_mapping/output.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\vscode\data-governance\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\vscode\data-governance\test\standard_mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42653EAF-45C2-42A0-95E5-5777A3B7D7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D13083F-A554-49BC-A743-E60CA10CD15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AH$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AG$43</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="268">
   <si>
     <t>上游信息</t>
   </si>
@@ -113,9 +113,6 @@
   </si>
   <si>
     <t>业务口径(选填)</t>
-  </si>
-  <si>
-    <t>格式化枚举值</t>
   </si>
   <si>
     <t>说明</t>
@@ -1207,15 +1204,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH43"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="31" max="31" width="13.375" customWidth="1"/>
-    <col min="32" max="32" width="13.5" customWidth="1"/>
-    <col min="33" max="33" width="16.5" customWidth="1"/>
+    <col min="30" max="30" width="13.375" customWidth="1"/>
+    <col min="31" max="31" width="13.5" customWidth="1"/>
+    <col min="32" max="32" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:33">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1249,17 +1246,16 @@
       <c r="AA1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3" t="s">
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AD1" s="3"/>
       <c r="AE1" s="3"/>
       <c r="AF1" s="3"/>
       <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-    </row>
-    <row r="2" spans="1:34">
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1339,54 +1335,54 @@
         <v>29</v>
       </c>
       <c r="AA2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB2" t="s">
         <v>30</v>
       </c>
-      <c r="AB2" t="s">
-        <v>268</v>
-      </c>
       <c r="AC2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD2" t="s">
         <v>31</v>
       </c>
-      <c r="AD2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AF2" t="s">
         <v>32</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>267</v>
       </c>
       <c r="AG2" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" ht="105" customHeight="1">
+    </row>
+    <row r="3" spans="1:33" ht="105" customHeight="1">
       <c r="J3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="V3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W3" s="1"/>
       <c r="Y3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" t="s">
         <v>43</v>
       </c>
       <c r="AD3" t="s">
@@ -1401,74 +1397,74 @@
       <c r="AG3" t="s">
         <v>47</v>
       </c>
-      <c r="AH3" t="s">
+    </row>
+    <row r="4" spans="1:33" ht="90" customHeight="1">
+      <c r="J4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" ht="90" customHeight="1">
-      <c r="J4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="R4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W4" s="1"/>
       <c r="Y4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC4" t="s">
         <v>52</v>
       </c>
-      <c r="AB4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
+        <v>265</v>
+      </c>
+      <c r="AG4" t="s">
         <v>53</v>
       </c>
-      <c r="AG4" t="s">
-        <v>266</v>
-      </c>
-      <c r="AH4" t="s">
+    </row>
+    <row r="5" spans="1:33" ht="120" customHeight="1">
+      <c r="J5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="5" spans="1:34" ht="120" customHeight="1">
-      <c r="J5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="V5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W5" s="1"/>
       <c r="Y5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD5" t="s">
         <v>58</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>44</v>
       </c>
       <c r="AE5" t="s">
         <v>59</v>
@@ -1479,38 +1475,38 @@
       <c r="AG5" t="s">
         <v>61</v>
       </c>
-      <c r="AH5" t="s">
+    </row>
+    <row r="6" spans="1:33" ht="120" customHeight="1">
+      <c r="J6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" ht="120" customHeight="1">
-      <c r="J6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Q6" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="R6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W6" s="1"/>
       <c r="Y6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD6" t="s">
         <v>66</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>44</v>
       </c>
       <c r="AE6" t="s">
         <v>67</v>
@@ -1521,80 +1517,80 @@
       <c r="AG6" t="s">
         <v>69</v>
       </c>
-      <c r="AH6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" ht="90" customHeight="1">
+    </row>
+    <row r="7" spans="1:33" ht="90" customHeight="1">
       <c r="J7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q7" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W7" s="1"/>
       <c r="Y7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD7" t="s">
         <v>75</v>
       </c>
-      <c r="AB7" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>44</v>
-      </c>
       <c r="AE7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF7" t="s">
         <v>76</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>72</v>
       </c>
       <c r="AG7" t="s">
         <v>77</v>
       </c>
-      <c r="AH7" t="s">
+    </row>
+    <row r="8" spans="1:33" ht="75" customHeight="1">
+      <c r="J8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" ht="75" customHeight="1">
-      <c r="J8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W8" s="1"/>
       <c r="Y8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD8" t="s">
         <v>83</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>44</v>
       </c>
       <c r="AE8" t="s">
         <v>84</v>
@@ -1605,38 +1601,38 @@
       <c r="AG8" t="s">
         <v>86</v>
       </c>
-      <c r="AH8" t="s">
+    </row>
+    <row r="9" spans="1:33" ht="75" customHeight="1">
+      <c r="J9" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" ht="75" customHeight="1">
-      <c r="J9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="R9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W9" s="1"/>
       <c r="Y9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD9" t="s">
         <v>91</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>44</v>
       </c>
       <c r="AE9" t="s">
         <v>92</v>
@@ -1647,596 +1643,596 @@
       <c r="AG9" t="s">
         <v>94</v>
       </c>
-      <c r="AH9" t="s">
+    </row>
+    <row r="10" spans="1:33" ht="75" customHeight="1">
+      <c r="J10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" ht="75" customHeight="1">
-      <c r="J10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O10" s="1" t="s">
+      <c r="P10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="R10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W10" s="1"/>
       <c r="Y10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD10" t="s">
         <v>98</v>
       </c>
-      <c r="AB10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>44</v>
-      </c>
       <c r="AE10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF10" t="s">
         <v>99</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>96</v>
       </c>
       <c r="AG10" t="s">
         <v>100</v>
       </c>
-      <c r="AH10" t="s">
+    </row>
+    <row r="11" spans="1:33" ht="90" customHeight="1">
+      <c r="J11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" ht="90" customHeight="1">
-      <c r="J11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="Q11" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="R11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W11" s="1"/>
       <c r="Y11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF11" t="s">
         <v>105</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>53</v>
       </c>
       <c r="AG11" t="s">
         <v>106</v>
       </c>
-      <c r="AH11" t="s">
+    </row>
+    <row r="12" spans="1:33" ht="90" customHeight="1">
+      <c r="J12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="12" spans="1:34" ht="90" customHeight="1">
-      <c r="J12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="1" t="s">
+      <c r="P12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="R12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W12" s="1"/>
       <c r="Y12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF12" t="s">
         <v>110</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>53</v>
       </c>
       <c r="AG12" t="s">
         <v>111</v>
       </c>
-      <c r="AH12" t="s">
+    </row>
+    <row r="13" spans="1:33" ht="120" customHeight="1">
+      <c r="J13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" ht="120" customHeight="1">
-      <c r="J13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="P13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W13" s="1"/>
       <c r="Y13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF13" t="s">
         <v>114</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>53</v>
       </c>
       <c r="AG13" t="s">
         <v>115</v>
       </c>
-      <c r="AH13" t="s">
+    </row>
+    <row r="14" spans="1:33" ht="120" customHeight="1">
+      <c r="J14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" ht="120" customHeight="1">
-      <c r="J14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="P14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W14" s="1"/>
       <c r="Y14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF14" t="s">
         <v>118</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>53</v>
       </c>
       <c r="AG14" t="s">
         <v>119</v>
       </c>
-      <c r="AH14" t="s">
+    </row>
+    <row r="15" spans="1:33" ht="120" customHeight="1">
+      <c r="J15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" ht="120" customHeight="1">
-      <c r="J15" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="P15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W15" s="1"/>
       <c r="Y15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF15" t="s">
         <v>122</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>53</v>
       </c>
       <c r="AG15" t="s">
         <v>123</v>
       </c>
-      <c r="AH15" t="s">
+    </row>
+    <row r="16" spans="1:33" ht="120" customHeight="1">
+      <c r="J16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" ht="120" customHeight="1">
-      <c r="J16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="P16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W16" s="1"/>
       <c r="Y16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF16" t="s">
         <v>126</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>53</v>
       </c>
       <c r="AG16" t="s">
         <v>127</v>
       </c>
-      <c r="AH16" t="s">
+    </row>
+    <row r="17" spans="10:33" ht="120" customHeight="1">
+      <c r="J17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="17" spans="10:34" ht="120" customHeight="1">
-      <c r="J17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="P17" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W17" s="1"/>
       <c r="Y17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF17" t="s">
         <v>130</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>53</v>
       </c>
       <c r="AG17" t="s">
         <v>131</v>
       </c>
-      <c r="AH17" t="s">
+    </row>
+    <row r="18" spans="10:33" ht="120" customHeight="1">
+      <c r="J18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="18" spans="10:34" ht="120" customHeight="1">
-      <c r="J18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="Q18" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="R18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W18" s="1"/>
       <c r="Y18" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF18" t="s">
         <v>136</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>53</v>
       </c>
       <c r="AG18" t="s">
         <v>137</v>
       </c>
-      <c r="AH18" t="s">
+    </row>
+    <row r="19" spans="10:33" ht="120" customHeight="1">
+      <c r="J19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="19" spans="10:34" ht="120" customHeight="1">
-      <c r="J19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="P19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q19" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="Q19" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="R19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W19" s="1"/>
       <c r="Y19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF19" t="s">
         <v>140</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>53</v>
       </c>
       <c r="AG19" t="s">
         <v>141</v>
       </c>
-      <c r="AH19" t="s">
+    </row>
+    <row r="20" spans="10:33" ht="120" customHeight="1">
+      <c r="J20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="20" spans="10:34" ht="120" customHeight="1">
-      <c r="J20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="P20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="Q20" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="R20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W20" s="1"/>
       <c r="Y20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF20" t="s">
         <v>144</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>53</v>
       </c>
       <c r="AG20" t="s">
         <v>145</v>
       </c>
-      <c r="AH20" t="s">
+    </row>
+    <row r="21" spans="10:33" ht="120" customHeight="1">
+      <c r="J21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O21" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="21" spans="10:34" ht="120" customHeight="1">
-      <c r="J21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="P21" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q21" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="Q21" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="R21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W21" s="1"/>
       <c r="Y21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF21" t="s">
         <v>148</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>53</v>
       </c>
       <c r="AG21" t="s">
         <v>149</v>
       </c>
-      <c r="AH21" t="s">
+    </row>
+    <row r="22" spans="10:33" ht="120" customHeight="1">
+      <c r="J22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="22" spans="10:34" ht="120" customHeight="1">
-      <c r="J22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="P22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q22" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="Q22" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="R22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W22" s="1"/>
       <c r="Y22" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF22" t="s">
         <v>152</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>53</v>
       </c>
       <c r="AG22" t="s">
         <v>153</v>
       </c>
-      <c r="AH22" t="s">
+    </row>
+    <row r="23" spans="10:33" ht="105" customHeight="1">
+      <c r="J23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="23" spans="10:34" ht="105" customHeight="1">
-      <c r="J23" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="P23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q23" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W23" s="1"/>
       <c r="Y23" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD23" t="s">
         <v>156</v>
       </c>
-      <c r="AB23" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>44</v>
-      </c>
       <c r="AE23" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF23" t="s">
         <v>157</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>155</v>
       </c>
       <c r="AG23" t="s">
         <v>158</v>
       </c>
-      <c r="AH23" t="s">
+    </row>
+    <row r="24" spans="10:33" ht="120" customHeight="1">
+      <c r="J24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="24" spans="10:34" ht="120" customHeight="1">
-      <c r="J24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="P24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Q24" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="R24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W24" s="1"/>
       <c r="Y24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC24" t="s">
         <v>161</v>
       </c>
-      <c r="AB24" t="s">
-        <v>43</v>
-      </c>
       <c r="AD24" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="AE24" t="s">
         <v>67</v>
       </c>
       <c r="AF24" t="s">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="AG24" t="s">
         <v>163</v>
       </c>
-      <c r="AH24" t="s">
+    </row>
+    <row r="25" spans="10:33" ht="120" customHeight="1">
+      <c r="J25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="25" spans="10:34" ht="120" customHeight="1">
-      <c r="J25" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O25" s="1" t="s">
+      <c r="P25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q25" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="R25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W25" s="1"/>
       <c r="Y25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD25" t="s">
         <v>167</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>44</v>
       </c>
       <c r="AE25" t="s">
         <v>168</v>
@@ -2247,34 +2243,34 @@
       <c r="AG25" t="s">
         <v>170</v>
       </c>
-      <c r="AH25" t="s">
+    </row>
+    <row r="26" spans="10:33" ht="105" customHeight="1">
+      <c r="J26" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="26" spans="10:34" ht="105" customHeight="1">
-      <c r="J26" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="O26" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W26" s="1"/>
       <c r="Y26" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="AB26" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC26" t="s">
         <v>43</v>
       </c>
       <c r="AD26" t="s">
@@ -2284,43 +2280,43 @@
         <v>45</v>
       </c>
       <c r="AF26" t="s">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="AG26" t="s">
         <v>178</v>
       </c>
-      <c r="AH26" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" spans="10:34" ht="120" customHeight="1">
+    </row>
+    <row r="27" spans="10:33" ht="120" customHeight="1">
       <c r="J27" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O27" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="P27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="R27" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W27" s="1"/>
       <c r="Y27" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD27" t="s">
         <v>183</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>44</v>
       </c>
       <c r="AE27" t="s">
         <v>184</v>
@@ -2331,38 +2327,38 @@
       <c r="AG27" t="s">
         <v>186</v>
       </c>
-      <c r="AH27" t="s">
+    </row>
+    <row r="28" spans="10:33" ht="120" customHeight="1">
+      <c r="J28" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O28" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="28" spans="10:34" ht="120" customHeight="1">
-      <c r="J28" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="P28" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W28" s="1"/>
       <c r="Y28" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD28" t="s">
         <v>189</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>44</v>
       </c>
       <c r="AE28" t="s">
         <v>190</v>
@@ -2373,38 +2369,38 @@
       <c r="AG28" t="s">
         <v>192</v>
       </c>
-      <c r="AH28" t="s">
+    </row>
+    <row r="29" spans="10:33" ht="90" customHeight="1">
+      <c r="J29" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="29" spans="10:34" ht="90" customHeight="1">
-      <c r="J29" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="P29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R29" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W29" s="1"/>
       <c r="Y29" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD29" t="s">
         <v>195</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>44</v>
       </c>
       <c r="AE29" t="s">
         <v>196</v>
@@ -2415,38 +2411,38 @@
       <c r="AG29" t="s">
         <v>198</v>
       </c>
-      <c r="AH29" t="s">
+    </row>
+    <row r="30" spans="10:33" ht="75" customHeight="1">
+      <c r="J30" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="30" spans="10:34" ht="75" customHeight="1">
-      <c r="J30" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="P30" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W30" s="1"/>
       <c r="Y30" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD30" t="s">
         <v>201</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>44</v>
       </c>
       <c r="AE30" t="s">
         <v>202</v>
@@ -2457,38 +2453,38 @@
       <c r="AG30" t="s">
         <v>204</v>
       </c>
-      <c r="AH30" t="s">
+    </row>
+    <row r="31" spans="10:33" ht="120" customHeight="1">
+      <c r="J31" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="31" spans="10:34" ht="120" customHeight="1">
-      <c r="J31" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="P31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q31" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q31" s="1" t="s">
+      <c r="R31" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R31" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W31" s="1"/>
       <c r="Y31" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD31" t="s">
         <v>207</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>44</v>
       </c>
       <c r="AE31" t="s">
         <v>208</v>
@@ -2499,194 +2495,194 @@
       <c r="AG31" t="s">
         <v>210</v>
       </c>
-      <c r="AH31" t="s">
+    </row>
+    <row r="32" spans="10:33" ht="120" customHeight="1">
+      <c r="J32" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="32" spans="10:34" ht="120" customHeight="1">
-      <c r="J32" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="O32" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q32" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="P32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="R32" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W32" s="1"/>
       <c r="Y32" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB32" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC32" t="s">
         <v>43</v>
       </c>
       <c r="AD32" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="AE32" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AF32" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s">
         <v>213</v>
       </c>
-      <c r="AH32" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="33" spans="10:34" ht="105" customHeight="1">
+    </row>
+    <row r="33" spans="10:33" ht="105" customHeight="1">
       <c r="J33" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O33" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q33" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="R33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W33" s="1"/>
       <c r="Y33" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>53</v>
+        <v>214</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>217</v>
       </c>
       <c r="AG33" t="s">
         <v>218</v>
       </c>
-      <c r="AH33" t="s">
+    </row>
+    <row r="34" spans="10:33" ht="105" customHeight="1">
+      <c r="J34" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="34" spans="10:34" ht="105" customHeight="1">
-      <c r="J34" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="P34" s="1" t="s">
+      <c r="Q34" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="Q34" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="R34" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W34" s="1"/>
       <c r="Y34" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF34" t="s">
         <v>223</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>53</v>
       </c>
       <c r="AG34" t="s">
         <v>224</v>
       </c>
-      <c r="AH34" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="35" spans="10:34" ht="90" customHeight="1">
+    </row>
+    <row r="35" spans="10:33" ht="90" customHeight="1">
       <c r="J35" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W35" s="1"/>
       <c r="Y35" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AB35" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC35" t="s">
         <v>43</v>
       </c>
       <c r="AD35" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="AE35" t="s">
         <v>202</v>
       </c>
       <c r="AF35" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="AG35" t="s">
         <v>227</v>
       </c>
-      <c r="AH35" t="s">
+    </row>
+    <row r="36" spans="10:33" ht="90" customHeight="1">
+      <c r="J36" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="36" spans="10:34" ht="90" customHeight="1">
-      <c r="J36" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="P36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q36" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="R36" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R36" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V36" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W36" s="1"/>
       <c r="Y36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD36" t="s">
         <v>230</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>44</v>
       </c>
       <c r="AE36" t="s">
         <v>231</v>
@@ -2697,38 +2693,38 @@
       <c r="AG36" t="s">
         <v>233</v>
       </c>
-      <c r="AH36" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="37" spans="10:34" ht="75" customHeight="1">
+    </row>
+    <row r="37" spans="10:33" ht="75" customHeight="1">
       <c r="J37" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W37" s="1"/>
       <c r="Y37" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD37" t="s">
         <v>235</v>
-      </c>
-      <c r="AB37" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>162</v>
       </c>
       <c r="AE37" t="s">
         <v>236</v>
@@ -2739,251 +2735,248 @@
       <c r="AG37" t="s">
         <v>238</v>
       </c>
-      <c r="AH37" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="38" spans="10:34" ht="75" customHeight="1">
+    </row>
+    <row r="38" spans="10:33" ht="75" customHeight="1">
       <c r="J38" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q38" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R38" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W38" s="1"/>
       <c r="Y38" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="AB38" t="s">
+        <v>239</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC38" t="s">
         <v>43</v>
       </c>
       <c r="AD38" t="s">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="AE38" t="s">
         <v>196</v>
       </c>
       <c r="AF38" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="AG38" t="s">
         <v>241</v>
       </c>
-      <c r="AH38" t="s">
+    </row>
+    <row r="39" spans="10:33" ht="105" customHeight="1">
+      <c r="J39" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O39" s="1" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="39" spans="10:34" ht="105" customHeight="1">
-      <c r="J39" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O39" s="1" t="s">
+      <c r="P39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q39" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="R39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W39" s="1"/>
       <c r="Y39" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF39" t="s">
         <v>245</v>
-      </c>
-      <c r="AB39" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>53</v>
       </c>
       <c r="AG39" t="s">
         <v>246</v>
       </c>
-      <c r="AH39" t="s">
+    </row>
+    <row r="40" spans="10:33" ht="90" customHeight="1">
+      <c r="J40" s="1" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="40" spans="10:34" ht="90" customHeight="1">
-      <c r="J40" s="1" t="s">
+      <c r="O40" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="P40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q40" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="P40" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="R40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W40" s="1"/>
       <c r="Y40" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF40" t="s">
         <v>251</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>53</v>
       </c>
       <c r="AG40" t="s">
         <v>252</v>
       </c>
-      <c r="AH40" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="41" spans="10:34" ht="105" customHeight="1">
+    </row>
+    <row r="41" spans="10:33" ht="105" customHeight="1">
       <c r="J41" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O41" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q41" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="P41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="R41" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W41" s="1"/>
       <c r="Y41" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>172</v>
+      </c>
+      <c r="AF41" t="s">
         <v>254</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>175</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>173</v>
       </c>
       <c r="AG41" t="s">
         <v>255</v>
       </c>
-      <c r="AH41" t="s">
+    </row>
+    <row r="42" spans="10:33" ht="105" customHeight="1">
+      <c r="J42" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="42" spans="10:34" ht="105" customHeight="1">
-      <c r="J42" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="O42" s="1" t="s">
+      <c r="P42" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="P42" s="1" t="s">
+      <c r="Q42" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="Q42" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="R42" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W42" s="1"/>
       <c r="Y42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD42" t="s">
         <v>260</v>
       </c>
-      <c r="AB42" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>44</v>
-      </c>
       <c r="AE42" t="s">
+        <v>256</v>
+      </c>
+      <c r="AF42" t="s">
         <v>261</v>
-      </c>
-      <c r="AF42" t="s">
-        <v>257</v>
       </c>
       <c r="AG42" t="s">
         <v>262</v>
       </c>
-      <c r="AH42" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="43" spans="10:34" ht="105" customHeight="1">
+    </row>
+    <row r="43" spans="10:33" ht="105" customHeight="1">
       <c r="J43" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O43" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q43" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="P43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="R43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W43" s="1"/>
       <c r="Y43" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB43" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD43" t="s">
-        <v>53</v>
+        <v>222</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF43" t="s">
+        <v>263</v>
       </c>
       <c r="AG43" t="s">
         <v>264</v>
       </c>
-      <c r="AH43" t="s">
-        <v>265</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AG43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
-    <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="I1:Z1"/>
-    <mergeCell ref="AD1:AH1"/>
+    <mergeCell ref="AC1:AG1"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="AA1:AB1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
